--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121300096</v>
+        <v>121300097</v>
       </c>
       <c r="B34" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590104</v>
+        <v>590087</v>
       </c>
       <c r="R34" t="n">
-        <v>6326110</v>
+        <v>6326115</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>30-40 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,10 +4605,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121300097</v>
+        <v>121300096</v>
       </c>
       <c r="B35" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590087</v>
+        <v>590104</v>
       </c>
       <c r="R35" t="n">
-        <v>6326115</v>
+        <v>6326110</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>30-40 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>121300097</v>
       </c>
       <c r="B34" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>121300096</v>
       </c>
       <c r="B35" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121300097</v>
+        <v>121300096</v>
       </c>
       <c r="B34" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590087</v>
+        <v>590104</v>
       </c>
       <c r="R34" t="n">
-        <v>6326115</v>
+        <v>6326110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>30-40 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,10 +4605,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121300096</v>
+        <v>121300097</v>
       </c>
       <c r="B35" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590104</v>
+        <v>590087</v>
       </c>
       <c r="R35" t="n">
-        <v>6326110</v>
+        <v>6326115</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>30-40 plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121300096</v>
+        <v>121300097</v>
       </c>
       <c r="B34" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590104</v>
+        <v>590087</v>
       </c>
       <c r="R34" t="n">
-        <v>6326110</v>
+        <v>6326115</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>30-40 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,10 +4605,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121300097</v>
+        <v>121300096</v>
       </c>
       <c r="B35" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590087</v>
+        <v>590104</v>
       </c>
       <c r="R35" t="n">
-        <v>6326115</v>
+        <v>6326110</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>30-40 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4484,7 +4484,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121300097</v>
+        <v>121300096</v>
       </c>
       <c r="B34" t="n">
         <v>98098</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590087</v>
+        <v>590104</v>
       </c>
       <c r="R34" t="n">
-        <v>6326115</v>
+        <v>6326110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>30-40 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,7 +4605,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121300096</v>
+        <v>121300097</v>
       </c>
       <c r="B35" t="n">
         <v>98098</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590104</v>
+        <v>590087</v>
       </c>
       <c r="R35" t="n">
-        <v>6326110</v>
+        <v>6326115</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>30-40 plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>121300096</v>
       </c>
       <c r="B34" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>121300097</v>
       </c>
       <c r="B35" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121300096</v>
+        <v>121300097</v>
       </c>
       <c r="B34" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590104</v>
+        <v>590087</v>
       </c>
       <c r="R34" t="n">
-        <v>6326110</v>
+        <v>6326115</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>30-40 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,10 +4605,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121300097</v>
+        <v>121300096</v>
       </c>
       <c r="B35" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590087</v>
+        <v>590104</v>
       </c>
       <c r="R35" t="n">
-        <v>6326115</v>
+        <v>6326110</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>30-40 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4484,7 +4484,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121300097</v>
+        <v>121300096</v>
       </c>
       <c r="B34" t="n">
         <v>98105</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590087</v>
+        <v>590104</v>
       </c>
       <c r="R34" t="n">
-        <v>6326115</v>
+        <v>6326110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>30-40 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,7 +4605,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121300096</v>
+        <v>121300097</v>
       </c>
       <c r="B35" t="n">
         <v>98105</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590104</v>
+        <v>590087</v>
       </c>
       <c r="R35" t="n">
-        <v>6326110</v>
+        <v>6326115</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>30-40 plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4484,7 +4484,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121300096</v>
+        <v>121300097</v>
       </c>
       <c r="B34" t="n">
         <v>98105</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590104</v>
+        <v>590087</v>
       </c>
       <c r="R34" t="n">
-        <v>6326110</v>
+        <v>6326115</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>30-40 plantor</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,7 +4605,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121300097</v>
+        <v>121300096</v>
       </c>
       <c r="B35" t="n">
         <v>98105</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590087</v>
+        <v>590104</v>
       </c>
       <c r="R35" t="n">
-        <v>6326115</v>
+        <v>6326110</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>30-40 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 38249-2023 artfynd.xlsx
+++ b/artfynd/A 38249-2023 artfynd.xlsx
@@ -4487,7 +4487,7 @@
         <v>121300096</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>121300097</v>
       </c>
       <c r="B35" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
